--- a/artfynd/A 45279-2025 artfynd.xlsx
+++ b/artfynd/A 45279-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,136 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133716123</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57148</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Middagsmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583472</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6997850</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ensam toppspelande tupp. Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet. Punkten är placerad på spelplatsens geometriska centrum.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Lorentzon</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Lorentzon</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45279-2025 artfynd.xlsx
+++ b/artfynd/A 45279-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133220898</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133220896</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133219812</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45279-2025 artfynd.xlsx
+++ b/artfynd/A 45279-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133220898</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133220897</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133220896</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133219812</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>133716123</v>
       </c>
       <c r="B6" t="n">
-        <v>57148</v>
+        <v>57155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45279-2025 artfynd.xlsx
+++ b/artfynd/A 45279-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133220898</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133220897</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133220896</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>133219812</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>133716123</v>
       </c>
       <c r="B6" t="n">
-        <v>57155</v>
+        <v>57165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
